--- a/www/download/COUNTRY.TUR.EXI382.xlsx
+++ b/www/download/COUNTRY.TUR.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Turquia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10857852760736</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10857852760736</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10857852760736</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10857852760736</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10857852760736</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10857852760736</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10857852760736</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10857852760736</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10857852760736</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10857852760736</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10857852760736</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10857852760736</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10857852760736</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10857852760736</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10857852760736</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10857852760736</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10857852760736</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10857852760736</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10857852760736</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10857852760736</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10857852760736</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10857852760736</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10857852760736</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10857852760736</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10857852760736</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10871840490798</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10871840490798</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>28.658</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>19.976</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>20.45</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>20.442</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>20.952</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>21.477</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>21.64</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>21.588</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>21.424</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>21.217</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>21.843</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>22.322</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>20.488</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>20.815</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>21.487</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>21.265</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>22.589</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>24.094</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>24.814</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>25.172</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>23.919</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>26.994</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>26.207</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>24.874</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>21.837</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>22.57</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>23.765</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>17.757</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>8.426</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>8.903</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>9.288</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>9.52</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>9.567</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10.568</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>10.237</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>10.712</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>10.795</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>11.158</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>12.222</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>12.117</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>12.634</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>13.22</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>12.763</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>13.755</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>14.867</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>15.614</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>15.658</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>15.118</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>16.367</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>16.276</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15.613</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>13.786</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13.92</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>14.636</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>72019.181</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>46852.384</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>48030.768</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>48359.994</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>49575.55</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>50716.349</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>52229.132</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>54444.554</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>54135.707</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>53545.698</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>55833.248</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>59372.597</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>55112.822</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>53512.02</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>55256.652</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>53701.25</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>55832.97</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>59143.827</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>61914.777</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>62781.656</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>60010.983</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>67361.218</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>65871.389</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>62634.648</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>54985.97</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>56407.236</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>59530.308</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>45957.691</t>
+          <t>84355070124.2299</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-3895.532</t>
+          <t>82636592394.0102</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-2692.026</t>
+          <t>77673498826.5697</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-907.89</t>
+          <t>78217361862.4237</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-905.65</t>
+          <t>87365141199.2437</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-1686.361</t>
+          <t>86878475114.3107</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2457.944</t>
+          <t>84603453674.5853</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-1160.758</t>
+          <t>96596366494.8995</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1675.207</t>
+          <t>92154869448.2911</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2812.846</t>
+          <t>104114612200.51</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3042.446</t>
+          <t>106974514868.056</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>6948.503</t>
+          <t>109095076354.256</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>11521.492</t>
+          <t>96240647817.1554</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>13079.198</t>
+          <t>103605190412.053</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>14780.236</t>
+          <t>78791985878.6134</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>13331.094</t>
+          <t>74356607765.0156</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>14524.008</t>
+          <t>86593955421.3666</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>16580.619</t>
+          <t>108330179728.256</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>18846.871</t>
+          <t>93692377177.038</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>40498.834</t>
+          <t>91974671362.4873</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>39248.991</t>
+          <t>83557434131.7984</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>42463.306</t>
+          <t>92271707714.479</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>42415.49</t>
+          <t>90369731467.4027</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>40657.082</t>
+          <t>86320140186.7713</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>35786.701</t>
+          <t>69336303881.4862</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>35857.209</t>
+          <t>79252073984.1715</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>37822.011</t>
+          <t>79457522355.0403</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>8424806936.18812</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>9241445727.37476</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>9828438856.8281</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>10104487823.1042</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>10549403328.2872</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>12261448914.9032</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>11446106052.91</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>13394523702.367</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>13675806254.0135</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>11268633477.1831</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>12591720671.5406</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>14151949727.8177</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>15689333514.1244</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>11599279107.5023</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>12840195691.1047</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>16572315745.9025</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>10912280495.7569</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>12856138978.8006</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>16624509681.7145</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>10195307207.4492</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>14608068593.3919</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>17049575724.9869</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>16572567556.4562</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15287272877.4049</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>11996253913.4249</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>8614963277.84141</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>12297210852.0169</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>72647411.7159474</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>27523428.4965108</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>23471973.816631</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>23692258.0704974</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>25762375.998628</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>18557402.3716151</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>24481571.9591253</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>23053265.3519649</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>21243437.75434</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>17810557.1979092</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>16340039.5699578</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>15807366.4553753</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>11669117.329031</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>11768294.5604643</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>12836875.4842316</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>8607419.18865432</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>11039806.7057442</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>10325660.3329777</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>9817984.2687775</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>15255337.8165813</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>12654076.0728858</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>14256153.1299599</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>14877480.095279</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14626081.2266027</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>12826162.1559568</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13760549.3362098</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>12320268.3596866</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>133326.535551664</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>253632.64166146</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>283880.837662982</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>290587.738434137</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>313000.915344429</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>378735.414064643</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>369292.383767033</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>383217.405197155</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>337986.668159811</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>322104.971657848</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>359127.108491775</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>394788.476887471</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>364871.471060206</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>352273.233121067</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>363551.658050102</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>396962.038512664</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>440817.025436357</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>522461.610154175</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>535531.707817454</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>529194.558807264</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>556374.820760488</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>578630.469727778</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>584639.755760195</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>545009.513306493</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>499624.96941265</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>496091.354908447</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>487605.54262187</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>314442.182222076</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>627961.450939684</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>642874.346016128</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>665546.918896261</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>784127.901569078</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>932102.954016223</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>911411.980959041</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1008720.76277969</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>884021.531502075</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>976014.289112067</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1075069.46033585</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1172805.87952506</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>1071919.88057997</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>1159498.47571678</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>883663.869682968</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>961680.756971697</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1165927.92653342</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1609932.62070181</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>1360130.29525275</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>1382033.3789358</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>1418316.18150237</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>1427575.9838761</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>1478185.88953218</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>1373220.03952234</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>1175241.38812844</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>1277896.66064745</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>1257865.03365172</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>4.45504385430462</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-1.42152841827244</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-1.27390168867821</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-1.08985017507999</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-1.0858484571841</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-1.13753358283479</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.785259372171257</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-1.08665914711442</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-0.877505796082311</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-0.750382687862434</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-0.758377263967008</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-0.509007371166229</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>-0.265648092085226</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.127587143887505</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.15109117925963</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>-0.195580496750504</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.330978250205526</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.289704399379171</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.133679811364445</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2.97230153443856</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>1.68680223854508</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>1.49057848241764</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>1.55937951457216</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>1.65953789397732</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>1.98315630848769</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>3.16220100856965</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2.07565766578098</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>474.450670864811</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1096.72525958522</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1103.88486065382</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1087.88439343463</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1108.10732214547</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1281.61310674964</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1083.132031201</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1308.45506963607</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1276.69286065164</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1043.91394560113</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1128.53307804032</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1157.92679702026</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1294.78790771212</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>918.085759882497</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>971.233742377984</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1298.47571836356</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>793.343450704888</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>864.737506225133</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1064.70454340997</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>651.137601265398</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>966.263444113143</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>1041.69367496576</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>1018.19048593334</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>979.122721822477</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>870.175756558364</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>618.887479099814</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>840.2079050899</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>3711435611.48739</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>4018577675.88789</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>1319074038.02846</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>1373919256.66936</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>1713565006.3783</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>2249560534.84571</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>582797092.714264</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>1785074241.15383</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>1412497642.50582</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>3292470901.05786</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>3893475961.59236</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>3007229510.85775</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>4114501195.67774</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>5242871445.9194</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>4134738301.85164</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>5959157605.39799</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>3003125086.33542</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>3936314584.83642</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>5145185611.56248</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>3782117253.96255</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>6337710574.69685</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>5544237538.38926</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.332</t>
+          <t>4471955187.80886</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>4142835679.03015</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>5676418608.38721</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>6341794064.42347</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>4862564139.74711</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1222866247.83241</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2730643907.10132</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-208304753.439618</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-337991400.340171</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>464232902.004876</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>869130289.417929</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-744610268.577539</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>846420164.905169</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>133657607.252339</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>1912427065.36884</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2440072164.3465</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2103052197.89561</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>3489531749.85119</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>4322753602.96616</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>2909658471.76262</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>5281292574.02609</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>2505661958.9828</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>3321664301.00628</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>4570598834.68684</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>3014623302.31424</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>5244207698.15124</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>4502804026.88921</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>3501073733.13724</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>3070324747.81907</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>4246145088.85765</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>4917030414.48995</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>5637725428.13904</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2488569363.65498</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1287933768.78656</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1527378791.46808</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1711910657.00953</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1249332104.37342</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>1380430245.42778</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1327407361.2918</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>938654076.24866</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1278840035.25348</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1380043835.68903</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>1453403797.24587</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>904177312.962145</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>624969445.826556</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>920117842.953246</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1225079830.08902</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>677865031.371899</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>497463127.352616</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>614650283.830138</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>574586776.875632</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>767493951.648303</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>1093502876.54561</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>1041433511.50005</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>970881454.671621</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>1072510931.21108</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>1430273519.52956</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>1424763649.93352</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-775161288.391926</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>2588.14921627179</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>-462.300863952386</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>-302.355927439393</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>-97.7466032168935</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>-95.1293040005957</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.519</t>
+          <t>-176.2648423793</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>232.592452401523</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.472</t>
+          <t>-113.389600372195</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>156.38747561292</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>260.578993203875</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.777</t>
+          <t>272.679250019836</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.854</t>
+          <t>568.533522066047</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.976</t>
+          <t>950.829970373373</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.022</t>
+          <t>1035.22169982969</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.839</t>
+          <t>1117.97859385062</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.069</t>
+          <t>1044.51919234755</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1.124</t>
+          <t>1055.92287783121</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1.354</t>
+          <t>1115.25576608673</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1.357</t>
+          <t>1207.03404593188</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>2586.51489263718</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>1.474</t>
+          <t>2596.15878466747</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>1.483</t>
+          <t>2594.41985214028</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>1.443</t>
+          <t>2605.93587163007</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>1.277</t>
+          <t>2604.01398154109</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>1.279</t>
+          <t>2595.87029767013</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2575.93408970038</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>1.409</t>
+          <t>2584.19188413953</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>2513.02471927088</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>2345.4924282244</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>2348.72726739375</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>2365.71734663867</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>2366.10364445176</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>2361.47011165585</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>2413.57930100809</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>2521.95894053178</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>2526.8838540141</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>2523.72863142167</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>2556.13968905023</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>2659.84808572807</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>2689.96559011772</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>2570.80224642427</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>2571.57193717266</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>2525.3113067364</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>2471.67749047124</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>2454.69146101461</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>2495.15503344863</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>2494.11687885323</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>2508.88834934573</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>2495.37647610672</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.332</t>
+          <t>2513.49629323156</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>2518.05339412071</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>2518.05635850873</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>2499.16725506746</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>2504.92772988721</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>35668.7807927079</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>43540.5029656918</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>56536.6848963677</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>59801.7058523782</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>53160.6326083829</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>68850.1712287499</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>74548.5851812646</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>76742.9861922067</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>74333.3090226108</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>87061.0392961734</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>100191.816593968</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>110983.05124617</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>119325.019502474</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>135287.25081714</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>123349.343840275</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>136794.009030661</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>149061.743671756</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>188145.575323427</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>191929.586999362</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>200757.424118152</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>220403.103409654</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>208306.548473262</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>228213.794071187</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>240535.393154922</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>262738.780422213</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>273790.877910107</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>285752.969702068</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>6003559244.26245</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>7900769182.42821</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>8810748342.0311</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>9116701291.85213</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>8573213687.41649</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>8550052680.23405</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>12664391963.2702</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>12922541598.7611</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>10427912657.9151</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>11638351759.1303</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>11350151564.1795</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>12040067366.0658</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>10745998744.2375</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>12890630493.1365</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>13110912175.873</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>10794206935.303</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>13063032034.4389</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>15737359050.277</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>15229883303.7751</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>16126978453.395</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>13653538717.0672</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>14419850240.2003</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>15930372894.9492</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>18258908518.7994</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>17279655143.2877</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>18947812725.293</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>19178607836.5731</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>36465.9493371022</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>47275.5564832146</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>58411.7699759479</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>56784.9300443146</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>53296.2418862964</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>78919.0939914481</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>61311.4752636829</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>69339.3227732725</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>75107.1891929922</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>93838.2379989792</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>112913.32171477</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>134040.52156968</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>145801.687637023</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>158690.403465637</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>123633.501826403</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>169805.062008392</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>206730.291852289</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>224981.429415587</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>238540.841714734</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>231774.593506996</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>241046.874304255</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>230516.563066785</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>264846.747337809</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>241722.320790371</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>237829.53137969</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>263917.232069419</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>284410.293569664</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>72019.181</t>
+          <t>10166611753.6114</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>46852.384</t>
+          <t>12678078342.0924</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>48030.768</t>
+          <t>10480815275.6369</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>48359.994</t>
+          <t>9922265052.87732</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>49575.55</t>
+          <t>10311655387.6427</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>50716.349</t>
+          <t>12361711716.1581</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>52229.132</t>
+          <t>11112321357.044</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>54444.554</t>
+          <t>13468734551.4811</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>54135.707</t>
+          <t>11971875250.6365</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>53545.698</t>
+          <t>16173692057.1241</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>55833.248</t>
+          <t>17371306690.6142</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>59372.597</t>
+          <t>18478057074.699</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>55112.822</t>
+          <t>18148436239.2517</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>53512.02</t>
+          <t>21340654753.0184</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>55256.652</t>
+          <t>17287476092.3611</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>53701.25</t>
+          <t>20823693935.8391</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>55832.97</t>
+          <t>22716249311.6695</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>59143.827</t>
+          <t>23689932171.7919</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>61914.777</t>
+          <t>25714553930.2703</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>62781.656</t>
+          <t>23206409786.7852</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>60010.983</t>
+          <t>21986776998.2727</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>67361.218</t>
+          <t>22319604896.296</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>65871.389</t>
+          <t>23930915139.2961</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>62634.648</t>
+          <t>22519712586.7439</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>54985.97</t>
+          <t>20682671203.7253</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>56407.236</t>
+          <t>24331455100.664</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>59530.308</t>
+          <t>23910348228.0203</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>45957.691</t>
+          <t>-797.168544394267</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-3895.532</t>
+          <t>-3735.0535175228</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>-2692.026</t>
+          <t>-1875.0850795802</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-907.89</t>
+          <t>3016.77580806359</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-905.65</t>
+          <t>-135.609277913601</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-1686.361</t>
+          <t>-10068.9227626982</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2457.944</t>
+          <t>13237.1099175817</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-1160.758</t>
+          <t>7403.66341893419</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1675.207</t>
+          <t>-773.88017038146</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2812.846</t>
+          <t>-6777.19870280576</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>3042.446</t>
+          <t>-12721.5051208024</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>6948.503</t>
+          <t>-23057.4703235098</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>11521.492</t>
+          <t>-26476.668134549</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>13079.198</t>
+          <t>-23403.152648497</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>14780.236</t>
+          <t>-284.157986127963</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>13331.094</t>
+          <t>-33011.0529777313</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>14524.008</t>
+          <t>-57668.5481805329</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>16580.619</t>
+          <t>-36835.8540921607</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>18846.871</t>
+          <t>-46611.254715372</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>40498.834</t>
+          <t>-31017.1693888445</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>39248.991</t>
+          <t>-20643.7708946011</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>42463.306</t>
+          <t>-22210.0145935235</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>42415.49</t>
+          <t>-36632.9532666219</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>40657.082</t>
+          <t>-1186.92763544856</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>35786.701</t>
+          <t>24909.2490425236</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>35857.209</t>
+          <t>9873.64584068788</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>37822.011</t>
+          <t>1342.6761324041</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>60398.763</t>
+          <t>-4163052509.34892</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>60049.814</t>
+          <t>-4777309159.6642</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>57439.722</t>
+          <t>-1670066933.60578</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>57559.308</t>
+          <t>-805563761.025192</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>61985.948</t>
+          <t>-1738441700.2262</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>63125.736</t>
+          <t>-3811659035.92408</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>61485.23</t>
+          <t>1552070606.22624</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>69612.078</t>
+          <t>-546192952.720062</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>66700.621</t>
+          <t>-1543962592.72134</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>73837.366</t>
+          <t>-4535340297.99384</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>76164.704</t>
+          <t>-6021155126.43468</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>77147.68</t>
+          <t>-6437989708.63326</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>70004.454</t>
+          <t>-7402437495.01417</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>73155.179</t>
+          <t>-8450024259.88192</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>58681.357</t>
+          <t>-4176563916.48813</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>55790.388</t>
+          <t>-10029487000.5361</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>63920.927</t>
+          <t>-9653217277.23055</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>77231.965</t>
+          <t>-7952573121.51488</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>69995.091</t>
+          <t>-10484670626.4952</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>68226.536</t>
+          <t>-7079431333.39016</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>62050.26</t>
+          <t>-8333238281.20556</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>68979.18</t>
+          <t>-7899754656.09571</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>67554.62</t>
+          <t>-8000542244.3469</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>64585.181</t>
+          <t>-4260804067.94451</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>52535.303</t>
+          <t>-3403016060.4376</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>58878.622</t>
+          <t>-5383642375.37107</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>58722.096</t>
+          <t>-4731740391.44719</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>27795.5836459503</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.389</t>
+          <t>34452.7619803309</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.408</t>
+          <t>40355.095670054</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.424</t>
+          <t>42689.6900561343</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.483</t>
+          <t>45035.719573455</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.588</t>
+          <t>61046.6368343201</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>49728.1991918335</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.633</t>
+          <t>63653.4248254679</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.558</t>
+          <t>76475.2954928845</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>98830.3607275341</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.668</t>
+          <t>131776.193666389</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.725</t>
+          <t>151881.57985386</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.679</t>
+          <t>177448.339907856</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>190672.350543041</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>167714.304154862</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.629</t>
+          <t>237688.322662139</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.751</t>
+          <t>247213.989570472</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1.001</t>
+          <t>275538.840191147</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.882</t>
+          <t>302028.697402983</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.883</t>
+          <t>306576.46114228</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.897</t>
+          <t>334337.67778873</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.905</t>
+          <t>342334.144502854</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>335821.301978468</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.864</t>
+          <t>296467.538970541</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.743</t>
+          <t>301865.700257927</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.794</t>
+          <t>296864.104338267</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.777</t>
+          <t>333194.411537037</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>35767.368</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>33376.79</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>34299.11</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>34150.87</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>34873.608</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>35300.773</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>34280.229</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>36697.38</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>35233.437</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>34359.983</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>35734.852</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>36723.451</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>32759.414</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>31476.829</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>32416.123</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>30692.878</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>32739.665</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>35155.732</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>36890.024</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>35218.032</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>32777.778</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>37399.916</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>35742.283</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>34259.111</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>29476.624</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>30766.391</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>30801.34</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>34792.3800870527</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>42860.7753386899</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>55134.1923077381</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>62520.4393987251</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>66714.7121048819</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>84515.2793093486</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>69224.4659629267</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>82979.8880707985</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>95424.7083036087</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>119090.144852509</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>154010.066580625</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>173496.119888216</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>201827.8134092</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>213782.414600877</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>189188.836016872</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>278511.825097177</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.385</t>
+          <t>268995.942474624</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>306564.602400625</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.465</t>
+          <t>329704.691368249</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>333115.00766892</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.474</t>
+          <t>368734.211039537</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.491</t>
+          <t>375892.907827243</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.492</t>
+          <t>367822.966698373</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.458</t>
+          <t>323647.51080707</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>340094.853939917</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>337056.712457589</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>394520.752459096</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>7444.215</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>8220.079</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>8908.096</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>9153.847</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>9561.525</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>10877.692</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>10054.321</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>11703.323</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>11910.188</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>9660.132</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>10896.957</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>12416.54</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>13326.109</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>9793.383</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>11382.075</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>14831.879</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>9715.358</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>11016.027</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>14675.032</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>9041.935</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>12863.442</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>15074.806</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>14585.618</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>13345.26</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>10790.315</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>7918.098</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>11289.807</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>517.36</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>-147.39</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-130.22</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-109.92</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-109.47</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-115.5</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>-75.55</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>-109.92</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>-85.93</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>-70.88</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>-72.08</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-44.04</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>-13.54</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>33.55</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>29.86</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>-10.12</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>49.5</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>50.51</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>28.43</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>347.9</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>205.12</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>181.68</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>190.8</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>204.66</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>231.66</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>352.85</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>235.01</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>73.706</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>26.367</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>23.042</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>23.054</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>23.991</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>17.57</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>23.29</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>21.704</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>20.187</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>16.399</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>15.379</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>14.789</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>11.242</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>10.893</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>12.449</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>8.375</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>10.626</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>9.766</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>9.604</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>15.092</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>12.545</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>14.213</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>14.818</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>14.538</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>12.911</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>13.631</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>12.283</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>146858.780241017</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>156983.825048275</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>184090.258609853</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>197098.981645874</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>186074.589697986</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>225972.746705105</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>166825.673691281</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>181035.337781524</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>192499.931244041</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>219919.180854608</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>263486.017185592</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>278707.53204288</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>303417.61364337</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>317619.456006461</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>287109.019155588</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>309252.157219988</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>338420.189303453</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>383996.161722687</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>395616.924718923</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>376987.645696564</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>415696.728683472</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>417408.467862102</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>395282.697435618</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>333716.804972829</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>341308.506233211</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>359996.255784021</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>317244.733926055</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>45957691300.9559</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>-3895532000.01085</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>-2692025999.95577</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-907889999.999569</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-905649999.946291</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-1686361000.01234</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2457943999.99627</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>-1160758000.05094</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1675207000.01794</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2812846000.03785</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>3042446000.02082</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>6948502999.98461</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>11521492000.0085</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>13079197999.9825</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>14780235999.9981</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>13331094000.0127</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>14524007999.9944</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>16580618999.9892</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>18846870999.9925</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>40498834464.2229</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>39248991397.5454</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>42463306435.0025</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>42415489907.8573</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>40657081513.03</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>35786700540.0537</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>35857208843.822</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>37822010824.7308</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>72019181052.972</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>46852384000.0098</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>48030768000.0083</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>48359993999.9976</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>49575550000.0098</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>50716348999.9947</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>52229132000.0077</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>54444553999.9951</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>54135707000.0118</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>53545697999.9976</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>55833247999.9837</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>59372597000.0011</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>55112822000.008</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>53512019999.9925</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>55256651999.9951</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>53701250000.0083</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>55832969999.9978</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>59143826999.9862</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>61914776999.9911</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>62781655630.7099</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>60010982570.6192</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>67361218305.7574</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>65871389148.0098</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>62634648393.5121</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>54985969939.7044</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>56407236288.7252</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>59530307947.6011</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>35767368030.5977</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>33376789602.9773</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>34299110001.4249</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>34150869975.5982</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>34873608131.8356</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>35300773486.3917</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>34280228628.9184</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>36697379775.9861</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>35233437387.6697</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>34359982826.1968</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>35734852141.4363</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>36723450812.9005</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>32759413628.781</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>31476829128.2277</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>32416123471.8209</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>30692878464.4028</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>32739665103.5797</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>35155732234.5845</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>36890023650.1036</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>35218031904.9846</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>32777777652.5409</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>37399915787.6327</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>35742282555.5029</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>34259110876.4365</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>29476624169.2194</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>30766391346.6933</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>30801339783.5226</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>28658365.5547437</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>19975500.0000056</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>20449699.9999942</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>20442000.0000042</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>20952399.9999994</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>21476600.0000028</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>21639699.9999929</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>21588200.0000027</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>21423899.9999997</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>21216899.9999949</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>21842799.999999</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>22321799.9999986</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>20488299.9999997</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>20815299.999999</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>21487499.999999</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>21265199.9999989</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>22589099.9999976</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>24094200.0000033</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>24813999.9999987</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>25171897.9824138</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>23919351.6069653</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>26994411.0440819</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>26207076.3045845</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>24874233.6202063</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>21836671.6669792</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>22570412.674202</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>23765279.6275609</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>17756971.2797153</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>8426400.00000533</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>8903499.99999714</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>9288200.00000428</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>9520199.9999981</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>9567200.00000625</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10567599.9999911</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>10236900.0000072</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>10711899.9999993</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>10794599.9999973</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>11157599.9999981</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>12221799.9999961</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>12117300.0000034</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>12634199.9999944</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>13220499.9999965</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>12762900.0000001</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>13754800.0000016</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>14867100.0000011</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>15614200.0000025</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>15657684.6240119</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>15118101.2615038</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>16367168.328585</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>16276490.2888134</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15613234.7219459</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>13786012.5647161</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13920080.0933508</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>14635914.2511294</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>72019181052.972</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>46852384000.0098</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>48030768000.0083</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>48359993999.9976</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>49575550000.0098</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>50716348999.9947</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>52229132000.0077</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>54444553999.9951</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>54135707000.0118</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>53545697999.9976</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>55833247999.9837</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>59372597000.0011</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>55112822000.008</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>53512019999.9925</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>55256651999.9951</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>53701250000.0083</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>55832969999.9978</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>59143826999.9862</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>61914776999.9911</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>62781655630.7099</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>60010982570.6192</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>67361218305.7574</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>65871389148.0098</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>62634648393.5121</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>54985969939.7044</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>56407236288.7252</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>59530307947.6011</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>45957691300.9559</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>-3895532000.01085</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>-2692025999.95577</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-907889999.999569</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-905649999.946291</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-1686361000.01234</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2457943999.99627</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>-1160758000.05094</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>1675207000.01794</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2812846000.03785</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>3042446000.02082</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>6948502999.98461</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>11521492000.0085</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>13079197999.9825</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>14780235999.9981</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>13331094000.0127</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>14524007999.9944</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>16580618999.9892</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>18846870999.9925</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>40498834464.2229</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>39248991397.5454</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>42463306435.0025</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>42415489907.8573</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>40657081513.03</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>35786700540.0537</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>35857208843.822</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>37822010824.7308</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>312237.983091917</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>363262.059993164</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>411322.15892173</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>434369.789683906</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>440842.6215799</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>574285.65014789</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>449566.81970937</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>522510.852948881</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>575846.87619086</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>691648.757016702</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>860622.334568401</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>945580.34585604</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1080683.82066387</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>1131846.88648862</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>929215.653803689</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1184403.83809137</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1245022.69166228</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1500110.84892661</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>1503522.68673979</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>1476808.38849374</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>1632194.094883</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>1643294.03593103</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>1598012.82363281</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>1414732.49964263</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>1416694.41271111</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>1505975.78754704</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>1561163.76940694</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>50605.8870448203</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>61023.6526470002</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>71313.6906549056</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>75431.6347299638</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>80335.9539079763</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>102930.565415755</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>82676.9376260663</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>100358.767777082</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>115516.880123903</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>144135.256527149</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>187276.159905342</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>212706.661142875</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>247231.174522565</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>262633.308427856</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>228573.918089793</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>340295.214886689</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>329058.439192716</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>375203.183765347</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>403233.01600755</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>405904.604736011</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>447219.307004977</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>452957.432281731</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>446984.71802667</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>396347.951355496</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>412090.486415926</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>415938.620446496</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>482404.24535284</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
